--- a/assurance/08-analyses/fmea/exports/review/pfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/pfmea-review.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$13</definedName>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -233,6 +233,17 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00E3E8EE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E3E8EE"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E3E8EE"/>
+      </bottom>
+    </border>
+    <border>
       <bottom style="thin">
         <color rgb="00E3E8EE"/>
       </bottom>
@@ -241,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -321,22 +332,53 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -741,7 +783,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.3 · draft</t>
+          <t>0.4 · draft</t>
         </is>
       </c>
     </row>
@@ -753,7 +795,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-003</t>
+          <t>BL-007</t>
         </is>
       </c>
     </row>
@@ -777,7 +819,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -829,7 +871,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -839,7 +881,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1196,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="127.5" customHeight="1">
+    <row r="3" ht="181.5" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <r>
@@ -1370,7 +1412,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>panda/SConscript defaults to DEBUG with ALLOW_DEBUG; LIONDRIVER_REFERENCE is opt-in and no build path sets it</t>
+            <t>The release is built with a bypass of the release defaults: PANDA_DEBUG_BUILD set (build_release.sh then builds the panda without RELEASE=1, with ALLOW_DEBUG) or RELEASE_VARIANT=upstream / an empty LIONDRIVER_REFERENCE, neither of which needs a recorded override. Up to BL-003 panda/SConscript defaulted to DEBUG and no build path set LIONDRIVER_REFERENCE; since BL-005 the root SConstruct and tools/release/release_variant.sh default to the reference build and build_release.sh builds the panda with RELEASE=1</t>
           </r>
           <r>
             <rPr>
@@ -1391,7 +1433,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• WP-P-10 §6 rule (RELEASE=1 with the LionDriver key); not implemented</t>
+            <t>• Technical defaults: SConstruct sets LIONDRIVER_REFERENCE=1 unless it is set; release_variant.sh selects the reference variant and refuses an unknown one; build_release.sh builds RELEASE=1 unless PANDA_DEBUG_BUILD is set. Proven in CI, but a variable bypasses them (O 5). Signing with a LionDriver key is PFM-002</t>
           </r>
           <r>
             <rPr>
@@ -1400,12 +1442,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/07-supporting/WP-P-10-release-management.md</t>
+   tools/release/release_variant.sh</t>
           </r>
         </is>
       </c>
       <c r="J3" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K3" s="34" t="inlineStr">
         <is>
@@ -1415,7 +1457,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• INS-17 reads the version string (human check); planned release check for RELEASE and absent ALLOW_DEBUG not implemented</t>
+            <t>• CI job panda reference release build (safety.yaml, WP-W-03 ATC-19): variant selection checks, then RELEASE=1 build and an assertion that every firmware compile carries -DLIONDRIVER_REFERENCE and none -DALLOW_DEBUG. Proven automated check at a later station (CI, not the publication step, and signed with the debug key), so D 5. At run time pandad refuses a car mode on a non-reference panda (TSR-619); INS-17 reads the version string (human check)</t>
           </r>
           <r>
             <rPr>
@@ -1424,12 +1466,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
+   .github/workflows/safety.yaml</t>
           </r>
         </is>
       </c>
       <c r="L3" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M3" s="36" t="inlineStr">
         <is>
@@ -1460,7 +1502,7 @@
       </c>
       <c r="O3" s="37" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P3" s="33" t="inlineStr"/>
@@ -1736,7 +1778,7 @@
           </r>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2004,7 +2046,7 @@
       <c r="L5" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="39" t="inlineStr">
+      <c r="M5" s="40" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2031,7 +2073,7 @@
           </r>
         </is>
       </c>
-      <c r="O5" s="37" t="inlineStr">
+      <c r="O5" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2336,7 +2378,7 @@
           </r>
         </is>
       </c>
-      <c r="O6" s="37" t="inlineStr">
+      <c r="O6" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2614,7 +2656,7 @@
           </r>
         </is>
       </c>
-      <c r="O7" s="37" t="inlineStr">
+      <c r="O7" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2892,7 +2934,7 @@
           </r>
         </is>
       </c>
-      <c r="O8" s="37" t="inlineStr">
+      <c r="O8" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2902,7 +2944,7 @@
       <c r="R8" s="38" t="inlineStr"/>
       <c r="S8" s="38" t="inlineStr"/>
     </row>
-    <row r="9" ht="100.5" customHeight="1">
+    <row r="9" ht="141" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
           <r>
@@ -3091,7 +3133,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Exact ECU firmware compare and DTC read are manual steps; the reference ECU versions are not recorded yet (WP-C-01 OI-1)</t>
+            <t>Exact ECU firmware compare is a manual step; the reference ECU versions are not recorded yet (WP-C-01 OI-1). Since BL-007 the EPS and ABS/VSC fault codes are read automatically at every stationary start and an active code or a failed read refuses engagement (TSR-629, DQ-132 A, vehicle_dtc.py; unit-tested with mocked UDS answers, not verified on the vehicle): that checks the car's health (AOU-09), not its configuration, so the rating is unchanged</t>
           </r>
         </is>
       </c>
@@ -3170,7 +3212,7 @@
           </r>
         </is>
       </c>
-      <c r="O9" s="37" t="inlineStr">
+      <c r="O9" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3448,7 +3490,7 @@
           </r>
         </is>
       </c>
-      <c r="O10" s="37" t="inlineStr">
+      <c r="O10" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3699,7 +3741,7 @@
           </r>
         </is>
       </c>
-      <c r="O11" s="37" t="inlineStr">
+      <c r="O11" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3946,7 +3988,7 @@
           </r>
         </is>
       </c>
-      <c r="O12" s="37" t="inlineStr">
+      <c r="O12" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3956,8 +3998,8 @@
       <c r="R12" s="38" t="inlineStr"/>
       <c r="S12" s="38" t="inlineStr"/>
     </row>
-    <row r="13" ht="100.5" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="13" ht="195" customHeight="1">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3979,7 +4021,7 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4001,7 +4043,7 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4100,16 +4142,16 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>HZ-005
 HZ-006</t>
         </is>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4132,32 +4174,141 @@
           </r>
         </is>
       </c>
-      <c r="G13" s="33" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Upstream default turns Experimental Mode on (B-06 open); parameters set by hand</t>
-          </r>
-        </is>
-      </c>
-      <c r="I13" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• D-08 decided; INS-19 parameter list (draft)</t>
+      <c r="H13" s="45" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>An assured setting (ExperimentalMode, LongitudinalPersonality, AlphaLongitudinalEnabled, the joystick and maneuver debug modes) is set by hand away from its reference value and the entry gate fails to refuse engagement. Up to BL-003 the upstream default turned Experimental Mode on (B-06) and parameters were set by hand only</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="45" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Technical controls in BL-007: ExperimentalMode defaults off (params_keys.h, chill-mode default); on the reference platform the item does not engage while any ASSURED_PARAMS setting differs from its assured value (#287, DQ-221 A) and a change made while engaged is held until disengagement (#342, DQ-403 A); the reference build neither registers nor ships the joystick and maneuver processes (DQ-131 A). Not bypassable without a code change (O 4)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/assured_config.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="45" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Automated check at the step itself: NO_ENTRY settingNotAssured at every engagement attempt; test_assured_config.py and test_reference_build.py in the CI unit_tests job, the release file list checked in the panda reference release build job. Targeted, not proven by mutation and not verified on the vehicle, so D 7. INS-19 parameter dump compared by hand</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_assured_config.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L13" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N13" s="45" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">PFM-ACT-008 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ship the reference parameter set as release defaults (Chill Mode, B-06; debug modes off; SSH off) and check it at boot</t>
+          </r>
+        </is>
+      </c>
+      <c r="O13" s="48" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="P13" s="44" t="inlineStr"/>
+      <c r="Q13" s="44" t="inlineStr"/>
+      <c r="R13" s="49" t="inlineStr"/>
+      <c r="S13" s="49" t="inlineStr"/>
+    </row>
+    <row r="14" ht="87" customHeight="1">
+      <c r="A14" s="50" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="n"/>
+      <c r="E14" s="50" t="n"/>
+      <c r="F14" s="50" t="n"/>
+      <c r="G14" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SSH enabled by hand and left on (SshEnabled defaults off); the entry gate does not check it</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• D-08 decided; INS-19 parameter list (draft); SshEnabled has no default value, so it is off until set</t>
           </r>
           <r>
             <rPr>
@@ -4170,10 +4321,10 @@
           </r>
         </is>
       </c>
-      <c r="J13" s="35" t="n">
+      <c r="J14" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="34" t="inlineStr">
+      <c r="K14" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4194,15 +4345,15 @@
           </r>
         </is>
       </c>
-      <c r="L13" s="35" t="n">
+      <c r="L14" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="36" t="inlineStr">
+      <c r="M14" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N13" s="34" t="inlineStr">
+      <c r="N14" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4224,278 +4375,9 @@
           </r>
         </is>
       </c>
-      <c r="O13" s="37" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P13" s="33" t="inlineStr"/>
-      <c r="Q13" s="33" t="inlineStr"/>
-      <c r="R13" s="38" t="inlineStr"/>
-      <c r="S13" s="38" t="inlineStr"/>
-    </row>
-    <row r="14" ht="87" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">PFM-SE-023
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>I4 Provisioning: software, firmware, parameters (INS-15..20)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">PFM-FN-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Provision the released software, panda firmware, models and parameter set</t>
-          </r>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Unvalidated lateral and longitudinal behaviour</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-007</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Unvalidated driving model</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Model files not those of the release</t>
-          </r>
-        </is>
-      </c>
-      <c r="D14" s="31" t="inlineStr">
-        <is>
-          <t>HZ-003
-HZ-007</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">PFM-012 · wrong_version
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Model weights on the device differ from the release</t>
-          </r>
-        </is>
-      </c>
-      <c r="G14" s="33" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Model files changed by an update or local edit</t>
-          </r>
-        </is>
-      </c>
-      <c r="I14" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Models pinned by LFS object id in the release tree (D-05)</t>
-          </r>
-        </is>
-      </c>
-      <c r="J14" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• INS-18 hash compare with the release record (manual, script not proven)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
-          </r>
-        </is>
-      </c>
-      <c r="L14" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="M14" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N14" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">PFM-ACT-006 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Write a configuration-check script for INS-18 and INS-21..24 that compares ECU FW versions, model hashes, carParams and pandaStates with the release record and refuses engagement on mismatch (TSR-803)</t>
-          </r>
-        </is>
-      </c>
       <c r="O14" s="37" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P14" s="33" t="inlineStr"/>
@@ -4513,16 +4395,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-SE-024
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>I5 Reference-configuration check (INS-21..24)</t>
+            <t xml:space="preserve">PFM-SE-023
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>I4 Provisioning: software, firmware, parameters (INS-15..20)</t>
           </r>
         </is>
       </c>
@@ -4535,16 +4417,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-FN-009
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Confirm that the item identifies the vehicle as the reference configuration and runs the reference safety mode</t>
+            <t xml:space="preserve">PFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provision the released software, panda firmware, models and parameter set</t>
           </r>
         </is>
       </c>
@@ -4565,7 +4447,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Wrong limits enforced</t>
+            <t>Unvalidated lateral and longitudinal behaviour</t>
           </r>
           <r>
             <rPr>
@@ -4591,7 +4473,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Contributes to HZ-005</t>
+            <t>Contributes to HZ-007</t>
           </r>
           <r>
             <rPr>
@@ -4617,7 +4499,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Wrong controller tuning and, without the lock, wrong envelope</t>
+            <t>Unvalidated driving model</t>
           </r>
           <r>
             <rPr>
@@ -4643,14 +4525,14 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>carParams not those of TOYOTA_COROLLA_TSS2 with parameter 73</t>
+            <t>Model files not those of the release</t>
           </r>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>HZ-002
-HZ-005</t>
+          <t>HZ-003
+HZ-007</t>
         </is>
       </c>
       <c r="E15" s="32" t="n">
@@ -4665,17 +4547,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-013 · wrong_configuration
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Item identifies the vehicle wrongly (fuzzy fingerprint or cached CarParams of another car)</t>
+            <t xml:space="preserve">PFM-012 · wrong_version
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Model weights on the device differ from the release</t>
           </r>
         </is>
       </c>
@@ -4692,7 +4574,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Fuzzy fingerprint accepted at runtime; CarParamsCache can skip the FW query</t>
+            <t>Model files changed by an update or local edit</t>
           </r>
         </is>
       </c>
@@ -4704,21 +4586,12 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Reference lock accepts only TOYOTA with parameter 73 (reference build only, panda#4)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   panda/board/reference_lock.h</t>
+            <t>• Models pinned by LFS object id in the release tree (D-05)</t>
           </r>
         </is>
       </c>
       <c r="J15" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" s="34" t="inlineStr">
         <is>
@@ -4728,7 +4601,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• INS-22/23 read carParams and pandaStates against the expected values (human check of logs)</t>
+            <t>• INS-18 hash compare with the release record (manual, script not proven)</t>
           </r>
           <r>
             <rPr>
@@ -4742,7 +4615,7 @@
         </is>
       </c>
       <c r="L15" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M15" s="36" t="inlineStr">
         <is>
@@ -4771,7 +4644,7 @@
           </r>
         </is>
       </c>
-      <c r="O15" s="37" t="inlineStr">
+      <c r="O15" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4791,16 +4664,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-SE-025
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>I6 Calibration, functional check and driver briefing (INS-25..30)</t>
+            <t xml:space="preserve">PFM-SE-024
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>I5 Reference-configuration check (INS-21..24)</t>
           </r>
         </is>
       </c>
@@ -4813,16 +4686,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-FN-010
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Calibrate, prove the stock PCS path and engagement transitions, and brief the driver</t>
+            <t xml:space="preserve">PFM-FN-009
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Confirm that the item identifies the vehicle as the reference configuration and runs the reference safety mode</t>
           </r>
         </is>
       </c>
@@ -4843,7 +4716,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stock AEB unavailable while the owner relies on it</t>
+            <t>Wrong limits enforced</t>
           </r>
           <r>
             <rPr>
@@ -4861,6 +4734,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -4869,7 +4768,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay or forwarding fault undetected</t>
+            <t>Wrong controller tuning and, without the lock, wrong envelope</t>
           </r>
           <r>
             <rPr>
@@ -4895,13 +4794,14 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>INS-27 skipped or done without log review</t>
+            <t>carParams not those of TOYOTA_COROLLA_TSS2 with parameter 73</t>
           </r>
         </is>
       </c>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>HZ-011</t>
+          <t>HZ-002
+HZ-005</t>
         </is>
       </c>
       <c r="E16" s="32" t="n">
@@ -4916,17 +4816,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-014 · step_omitted
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Stock PCS path not verified after installation</t>
+            <t xml:space="preserve">PFM-013 · wrong_configuration
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item identifies the vehicle wrongly (fuzzy fingerprint or cached CarParams of another car)</t>
           </r>
         </is>
       </c>
@@ -4943,7 +4843,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Log review of forwarded and intercepted messages is manual and needs tools the installer may not have</t>
+            <t>Fuzzy fingerprint accepted at runtime; CarParamsCache can skip the FW query</t>
           </r>
         </is>
       </c>
@@ -4955,7 +4855,31 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• INS-27 instruction (draft)</t>
+            <t>• Reference lock accepts only TOYOTA with parameter 73 (reference build only, panda#4)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/board/reference_lock.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• INS-22/23 read carParams and pandaStates against the expected values (human check of logs)</t>
           </r>
           <r>
             <rPr>
@@ -4968,32 +4892,8 @@
           </r>
         </is>
       </c>
-      <c r="J16" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• relayMalfunction alert covers only the relay-not-intercepting case</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/safety.h</t>
-          </r>
-        </is>
-      </c>
-      <c r="L16" s="40" t="n">
-        <v>9</v>
+      <c r="L16" s="35" t="n">
+        <v>6</v>
       </c>
       <c r="M16" s="36" t="inlineStr">
         <is>
@@ -5009,20 +4909,20 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-ACT-009 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Provide a log-analysis tool for INS-27 that proves forwarding of stock PCS messages and blocking of intercepted ones</t>
-          </r>
-        </is>
-      </c>
-      <c r="O16" s="37" t="inlineStr">
+            <t xml:space="preserve">PFM-ACT-006 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Write a configuration-check script for INS-18 and INS-21..24 that compares ECU FW versions, model hashes, carParams and pandaStates with the release record and refuses engagement on mismatch (TSR-803)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O16" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5094,7 +4994,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Late or no driver intervention</t>
+            <t>Stock AEB unavailable while the owner relies on it</t>
           </r>
           <r>
             <rPr>
@@ -5112,15 +5012,15 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-007</t>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Relay or forwarding fault undetected</t>
           </r>
           <r>
             <rPr>
@@ -5138,32 +5038,6 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver's process model wrong (expects stops at lights, misreads override)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">Local  </t>
           </r>
           <r>
@@ -5172,14 +5046,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>INS-30 acknowledgement missing</t>
+            <t>INS-27 skipped or done without log review</t>
           </r>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>HZ-012
-HZ-007</t>
+          <t>HZ-011</t>
         </is>
       </c>
       <c r="E17" s="32" t="n">
@@ -5194,17 +5067,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-015 · step_omitted
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver not briefed on the item's limits and Chill Mode behaviour</t>
+            <t xml:space="preserve">PFM-014 · step_omitted
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock PCS path not verified after installation</t>
           </r>
         </is>
       </c>
@@ -5221,7 +5094,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>User information (WP-O-03) not yet written for the reference configuration</t>
+            <t>Log review of forwarded and intercepted messages is manual and needs tools the installer may not have</t>
           </r>
         </is>
       </c>
@@ -5233,7 +5106,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• INS-30 instruction (draft)</t>
+            <t>• INS-27 instruction (draft)</t>
           </r>
           <r>
             <rPr>
@@ -5254,10 +5127,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Signed acknowledgement (human)</t>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• relayMalfunction alert covers only the relay-not-intercepting case</t>
           </r>
           <r>
             <rPr>
@@ -5266,12 +5139,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
-          </r>
-        </is>
-      </c>
-      <c r="L17" s="35" t="n">
-        <v>8</v>
+   opendbc_repo/opendbc/safety/safety.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="L17" s="51" t="n">
+        <v>9</v>
       </c>
       <c r="M17" s="36" t="inlineStr">
         <is>
@@ -5287,20 +5160,20 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-ACT-010 · prevention
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Write the user information for the reference configuration (WP-O-03), covering Chill Mode limits and override behaviour</t>
-          </r>
-        </is>
-      </c>
-      <c r="O17" s="37" t="inlineStr">
+            <t xml:space="preserve">PFM-ACT-009 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide a log-analysis tool for INS-27 that proves forwarding of stock PCS messages and blocking of intercepted ones</t>
+          </r>
+        </is>
+      </c>
+      <c r="O17" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5320,16 +5193,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-SE-030
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>U1 Software update and rollback (WP-P-10 §8, WP-O-02)</t>
+            <t xml:space="preserve">PFM-SE-025
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>I6 Calibration, functional check and driver briefing (INS-25..30)</t>
           </r>
         </is>
       </c>
@@ -5342,16 +5215,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-FN-011
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Update or roll back only to an approved release whose evidence is valid for the installed device</t>
+            <t xml:space="preserve">PFM-FN-010
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Calibrate, prove the stock PCS path and engagement transitions, and brief the driver</t>
           </r>
         </is>
       </c>
@@ -5372,7 +5245,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unassured configuration driven</t>
+            <t>Late or no driver intervention</t>
           </r>
           <r>
             <rPr>
@@ -5398,7 +5271,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Contributes to HZ-005</t>
+            <t>Contributes to HZ-007</t>
           </r>
           <r>
             <rPr>
@@ -5424,7 +5297,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unverified software and possibly panda firmware installed</t>
+            <t>Driver's process model wrong (expects stops at lights, misreads override)</t>
           </r>
           <r>
             <rPr>
@@ -5450,14 +5323,14 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Update fetched from an uncontrolled branch</t>
+            <t>INS-30 acknowledgement missing</t>
           </r>
         </is>
       </c>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>HZ-002
-HZ-005</t>
+          <t>HZ-012
+HZ-007</t>
         </is>
       </c>
       <c r="E18" s="32" t="n">
@@ -5472,17 +5345,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-016 · wrong_version
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Device updates to software that is not an approved LionDriver release</t>
+            <t xml:space="preserve">PFM-015 · step_omitted
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not briefed on the item's limits and Chill Mode behaviour</t>
           </r>
         </is>
       </c>
@@ -5499,7 +5372,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Updates are git fetches from a configurable branch with no signature check beyond TLS (GAP-26)</t>
+            <t>User information (WP-O-03) not yet written for the reference configuration</t>
           </r>
         </is>
       </c>
@@ -5511,7 +5384,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• LionDriver controls its release branch (planned)</t>
+            <t>• INS-30 instruction (draft)</t>
           </r>
           <r>
             <rPr>
@@ -5520,7 +5393,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/07-supporting/WP-P-10-release-management.md</t>
+   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
           </r>
         </is>
       </c>
@@ -5532,15 +5405,24 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• None at the device; next installation check only</t>
-          </r>
-        </is>
-      </c>
-      <c r="L18" s="40" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Signed acknowledgement (human)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="L18" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="M18" s="36" t="inlineStr">
         <is>
@@ -5556,20 +5438,20 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-ACT-011 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Signed updates from a LionDriver-controlled branch, and a bench-tested rollback procedure for the device side (GAP-26, WP-S-07, WP-O-02)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O18" s="37" t="inlineStr">
+            <t xml:space="preserve">PFM-ACT-010 · prevention
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Write the user information for the reference configuration (WP-O-03), covering Chill Mode limits and override behaviour</t>
+          </r>
+        </is>
+      </c>
+      <c r="O18" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5641,7 +5523,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unverified combination in the vehicle</t>
+            <t>Unassured configuration driven</t>
           </r>
           <r>
             <rPr>
@@ -5659,6 +5541,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -5667,7 +5575,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Envelope behaviour not the one verified with that host</t>
+            <t>Unverified software and possibly panda firmware installed</t>
           </r>
           <r>
             <rPr>
@@ -5693,13 +5601,14 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Host software and panda firmware from different releases</t>
+            <t>Update fetched from an uncontrolled branch</t>
           </r>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>HZ-002</t>
+          <t>HZ-002
+HZ-005</t>
         </is>
       </c>
       <c r="E19" s="32" t="n">
@@ -5714,17 +5623,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">PFM-017 · wrong_sequence
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Rollback to a release whose evidence does not cover the installed panda firmware</t>
+            <t xml:space="preserve">PFM-016 · wrong_version
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Device updates to software that is not an approved LionDriver release</t>
           </r>
         </is>
       </c>
@@ -5741,7 +5650,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Rollback procedure for the device side not defined yet (WP-O-02)</t>
+            <t>Updates are git fetches from a configurable branch with no signature check beyond TLS (GAP-26)</t>
           </r>
         </is>
       </c>
@@ -5753,7 +5662,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• WP-P-10 §8 rule: rollback only to a release valid for the installed device</t>
+            <t>• LionDriver controls its release branch (planned)</t>
           </r>
           <r>
             <rPr>
@@ -5767,31 +5676,22 @@
         </is>
       </c>
       <c r="J19" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• pandad reflashes panda firmware that does not match the host tree</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/pandad/pandad.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L19" s="35" t="n">
-        <v>7</v>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• None at the device; next installation check only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L19" s="51" t="n">
+        <v>10</v>
       </c>
       <c r="M19" s="36" t="inlineStr">
         <is>
@@ -5820,7 +5720,7 @@
           </r>
         </is>
       </c>
-      <c r="O19" s="37" t="inlineStr">
+      <c r="O19" s="39" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5830,16 +5730,273 @@
       <c r="R19" s="38" t="inlineStr"/>
       <c r="S19" s="38" t="inlineStr"/>
     </row>
+    <row r="20" ht="87" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">PFM-SE-030
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>U1 Software update and rollback (WP-P-10 §8, WP-O-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">PFM-FN-011
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Update or roll back only to an approved release whose evidence is valid for the installed device</t>
+          </r>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unverified combination in the vehicle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Envelope behaviour not the one verified with that host</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Host software and panda firmware from different releases</t>
+          </r>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>HZ-002</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">PFM-017 · wrong_sequence
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Rollback to a release whose evidence does not cover the installed panda firmware</t>
+          </r>
+        </is>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Rollback procedure for the device side not defined yet (WP-O-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I20" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• WP-P-10 §8 rule: rollback only to a release valid for the installed device</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/07-supporting/WP-P-10-release-management.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• pandad reflashes panda firmware that does not match the host tree</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/pandad/pandad.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L20" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N20" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">PFM-ACT-011 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Signed updates from a LionDriver-controlled branch, and a bench-tested rollback procedure for the device side (GAP-26, WP-S-07, WP-O-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O20" s="39" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P20" s="33" t="inlineStr"/>
+      <c r="Q20" s="33" t="inlineStr"/>
+      <c r="R20" s="38" t="inlineStr"/>
+      <c r="S20" s="38" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S19"/>
-  <mergeCells count="4">
+  <autoFilter ref="A2:S20"/>
+  <mergeCells count="10">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="I1:M1"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5847,7 +6004,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LPFMEA — build, release, install, calibration, OTA · rev 0.3 · BL-003&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LPFMEA — build, release, install, calibration, OTA · rev 0.4 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5877,442 +6034,451 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="41" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="41" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="41" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="41" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="41" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="41" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="41" t="inlineStr">
+      <c r="H1" s="52" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="41" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+    <row r="2" ht="127.5" customHeight="1">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>PFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>Make RELEASE=1 LIONDRIVER_REFERENCE=1 with the LionDriver key the only release build, and add an automated release check (version contains RELEASE, ALLOW_DEBUG absent, reference lock present) that blocks publication (WP-P-10 §6; SW FMEA SWF-ACT-009)</t>
         </is>
       </c>
-      <c r="D2" s="42" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="F2" s="53" t="inlineStr">
+        <is>
+          <t>PFM-001.C1</t>
+        </is>
+      </c>
+      <c r="G2" s="53" t="inlineStr"/>
+      <c r="H2" s="53" t="inlineStr"/>
+      <c r="I2" s="53" t="inlineStr">
+        <is>
+          <t>In BL-007: the reference variant is the default (SConstruct, tools/release/release_variant.sh), build_release.sh builds the panda with RELEASE=1, and the CI job panda reference release build asserts -DLIONDRIVER_REFERENCE on every firmware compile and no -DALLOW_DEBUG. Open: the LionDriver release key (PFM-ACT-002), removing the PANDA_DEBUG_BUILD and RELEASE_VARIANT=upstream bypasses from release builds or recording their use, and a check that blocks publication rather than a CI job</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="33" customHeight="1">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>PFM-ACT-002</t>
+        </is>
+      </c>
+      <c r="B3" s="53" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C3" s="53" t="inlineStr">
+        <is>
+          <t>Generate the LionDriver release key offline and define the signing procedure (D-09); remove the debug key from release builds</t>
+        </is>
+      </c>
+      <c r="D3" s="53" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="42" t="inlineStr">
-        <is>
-          <t>PFM-001.C1</t>
-        </is>
-      </c>
-      <c r="G2" s="42" t="inlineStr"/>
-      <c r="H2" s="42" t="inlineStr"/>
-      <c r="I2" s="42" t="inlineStr"/>
-    </row>
-    <row r="3" ht="33" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
-        <is>
-          <t>PFM-ACT-002</t>
-        </is>
-      </c>
-      <c r="B3" s="42" t="inlineStr">
-        <is>
-          <t>design change</t>
-        </is>
-      </c>
-      <c r="C3" s="42" t="inlineStr">
-        <is>
-          <t>Generate the LionDriver release key offline and define the signing procedure (D-09); remove the debug key from release builds</t>
-        </is>
-      </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="F3" s="53" t="inlineStr">
+        <is>
+          <t>PFM-002.C1</t>
+        </is>
+      </c>
+      <c r="G3" s="53" t="inlineStr"/>
+      <c r="H3" s="53" t="inlineStr"/>
+      <c r="I3" s="53" t="inlineStr"/>
+    </row>
+    <row r="4" ht="33" customHeight="1">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>PFM-ACT-003</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>Build the HIL bench (D-04) and define the evidence package location and contents (WP-P-10 §5, OI-2) before the first vehicle-test baseline</t>
+        </is>
+      </c>
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="42" t="inlineStr">
-        <is>
-          <t>PFM-002.C1</t>
-        </is>
-      </c>
-      <c r="G3" s="42" t="inlineStr"/>
-      <c r="H3" s="42" t="inlineStr"/>
-      <c r="I3" s="42" t="inlineStr"/>
-    </row>
-    <row r="4" ht="33" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>PFM-ACT-003</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>Build the HIL bench (D-04) and define the evidence package location and contents (WP-P-10 §5, OI-2) before the first vehicle-test baseline</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>Jherrod Thomas</t>
-        </is>
-      </c>
-      <c r="E4" s="42" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="53" t="inlineStr">
         <is>
           <t>PFM-003.C1
 PFM-004.C1</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr"/>
-      <c r="H4" s="42" t="inlineStr"/>
-      <c r="I4" s="42" t="inlineStr"/>
+      <c r="G4" s="53" t="inlineStr"/>
+      <c r="H4" s="53" t="inlineStr"/>
+      <c r="I4" s="53" t="inlineStr"/>
     </row>
     <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>PFM-ACT-004</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Set up the LionDriver release channel and an installer that installs only signed release tags and records the installed commit (INS-15)</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>PFM-005.C1</t>
         </is>
       </c>
-      <c r="G5" s="42" t="inlineStr"/>
-      <c r="H5" s="42" t="inlineStr"/>
-      <c r="I5" s="42" t="inlineStr"/>
+      <c r="G5" s="53" t="inlineStr"/>
+      <c r="H5" s="53" t="inlineStr"/>
+      <c r="I5" s="53" t="inlineStr"/>
     </row>
     <row r="6" ht="46.5" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>PFM-ACT-005</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>Turn WP-O-01 into a recorded checklist (R-DEV, R-INS) with photos and sign-off, and include harness approval list, latch check and airbag-zone routing diagram for the reference vehicle</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="42" t="inlineStr">
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>PFM-006.C1
 PFM-008.C1
 PFM-010.C1</t>
         </is>
       </c>
-      <c r="G6" s="42" t="inlineStr"/>
-      <c r="H6" s="42" t="inlineStr"/>
-      <c r="I6" s="42" t="inlineStr"/>
+      <c r="G6" s="53" t="inlineStr"/>
+      <c r="H6" s="53" t="inlineStr"/>
+      <c r="I6" s="53" t="inlineStr"/>
     </row>
     <row r="7" ht="46.5" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>PFM-ACT-006</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>Write a configuration-check script for INS-18 and INS-21..24 that compares ECU FW versions, model hashes, carParams and pandaStates with the release record and refuses engagement on mismatch (TSR-803)</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="42" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>PFM-007.C1
 PFM-012.C1
 PFM-013.C1</t>
         </is>
       </c>
-      <c r="G7" s="42" t="inlineStr"/>
-      <c r="H7" s="42" t="inlineStr"/>
-      <c r="I7" s="42" t="inlineStr"/>
+      <c r="G7" s="53" t="inlineStr"/>
+      <c r="H7" s="53" t="inlineStr"/>
+      <c r="I7" s="53" t="inlineStr"/>
     </row>
     <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>PFM-ACT-007</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>Define the mount position and attitude tolerance band (WP-O-01 OI-2) and check the converged calibration against it</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F8" s="42" t="inlineStr">
+      <c r="F8" s="53" t="inlineStr">
         <is>
           <t>PFM-009.C1</t>
         </is>
       </c>
-      <c r="G8" s="42" t="inlineStr"/>
-      <c r="H8" s="42" t="inlineStr"/>
-      <c r="I8" s="42" t="inlineStr"/>
-    </row>
-    <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="G8" s="53" t="inlineStr"/>
+      <c r="H8" s="53" t="inlineStr"/>
+      <c r="I8" s="53" t="inlineStr"/>
+    </row>
+    <row r="9" ht="87" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>PFM-ACT-008</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>Ship the reference parameter set as release defaults (Chill Mode, B-06; debug modes off; SSH off) and check it at boot</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>PFM-011.C1
+PFM-011.C2</t>
+        </is>
+      </c>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="53" t="inlineStr"/>
+      <c r="I9" s="53" t="inlineStr">
+        <is>
+          <t>In BL-007: Experimental Mode off by default, every assured setting checked at each engagement on the reference platform (#287, test_assured_config.py), debug processes left out of the reference build (DQ-131 A, test_reference_build.py). Open: SSH (PFM-011.C2) is not checked, and the check is at engagement, not at boot</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>PFM-ACT-009</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>Provide a log-analysis tool for INS-27 that proves forwarding of stock PCS messages and blocking of intercepted ones</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="42" t="inlineStr">
-        <is>
-          <t>PFM-011.C1</t>
-        </is>
-      </c>
-      <c r="G9" s="42" t="inlineStr"/>
-      <c r="H9" s="42" t="inlineStr"/>
-      <c r="I9" s="42" t="inlineStr"/>
-    </row>
-    <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
-        <is>
-          <t>PFM-ACT-009</t>
-        </is>
-      </c>
-      <c r="B10" s="42" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="C10" s="42" t="inlineStr">
-        <is>
-          <t>Provide a log-analysis tool for INS-27 that proves forwarding of stock PCS messages and blocking of intercepted ones</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="F10" s="53" t="inlineStr">
+        <is>
+          <t>PFM-014.C1</t>
+        </is>
+      </c>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="53" t="inlineStr"/>
+      <c r="I10" s="53" t="inlineStr"/>
+    </row>
+    <row r="11" ht="33" customHeight="1">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>PFM-ACT-010</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>prevention</t>
+        </is>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>Write the user information for the reference configuration (WP-O-03), covering Chill Mode limits and override behaviour</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F10" s="42" t="inlineStr">
-        <is>
-          <t>PFM-014.C1</t>
-        </is>
-      </c>
-      <c r="G10" s="42" t="inlineStr"/>
-      <c r="H10" s="42" t="inlineStr"/>
-      <c r="I10" s="42" t="inlineStr"/>
-    </row>
-    <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>PFM-ACT-010</t>
-        </is>
-      </c>
-      <c r="B11" s="42" t="inlineStr">
-        <is>
-          <t>prevention</t>
-        </is>
-      </c>
-      <c r="C11" s="42" t="inlineStr">
-        <is>
-          <t>Write the user information for the reference configuration (WP-O-03), covering Chill Mode limits and override behaviour</t>
-        </is>
-      </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="F11" s="53" t="inlineStr">
+        <is>
+          <t>PFM-015.C1</t>
+        </is>
+      </c>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="53" t="inlineStr"/>
+      <c r="I11" s="53" t="inlineStr"/>
+    </row>
+    <row r="12" ht="33" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>PFM-ACT-011</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="inlineStr">
+        <is>
+          <t>Signed updates from a LionDriver-controlled branch, and a bench-tested rollback procedure for the device side (GAP-26, WP-S-07, WP-O-02)</t>
+        </is>
+      </c>
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F11" s="42" t="inlineStr">
-        <is>
-          <t>PFM-015.C1</t>
-        </is>
-      </c>
-      <c r="G11" s="42" t="inlineStr"/>
-      <c r="H11" s="42" t="inlineStr"/>
-      <c r="I11" s="42" t="inlineStr"/>
-    </row>
-    <row r="12" ht="33" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>PFM-ACT-011</t>
-        </is>
-      </c>
-      <c r="B12" s="42" t="inlineStr">
-        <is>
-          <t>design change</t>
-        </is>
-      </c>
-      <c r="C12" s="42" t="inlineStr">
-        <is>
-          <t>Signed updates from a LionDriver-controlled branch, and a bench-tested rollback procedure for the device side (GAP-26, WP-S-07, WP-O-02)</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
-        <is>
-          <t>Jherrod Thomas</t>
-        </is>
-      </c>
-      <c r="E12" s="42" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F12" s="42" t="inlineStr">
+      <c r="F12" s="53" t="inlineStr">
         <is>
           <t>PFM-016.C1
 PFM-017.C1</t>
         </is>
       </c>
-      <c r="G12" s="42" t="inlineStr"/>
-      <c r="H12" s="42" t="inlineStr"/>
-      <c r="I12" s="42" t="inlineStr"/>
+      <c r="G12" s="53" t="inlineStr"/>
+      <c r="H12" s="53" t="inlineStr"/>
+      <c r="I12" s="53" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I12"/>
@@ -6337,343 +6503,343 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="41" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="41" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="41" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="41" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>Producing the as-driven reference configuration (AC-001)</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>process_item</t>
         </is>
       </c>
-      <c r="D2" s="42" t="inlineStr"/>
-      <c r="E2" s="42" t="inlineStr"/>
+      <c r="D2" s="53" t="inlineStr"/>
+      <c r="E2" s="53" t="inlineStr"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-010</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    R1 Freeze and pin the baseline (WP-P-10 §4 steps 1-3)</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-001: Freeze every component of the release at an identified, protected version</t>
         </is>
       </c>
     </row>
     <row r="4" ht="33" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-011</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    R2 Build the release (host tree, panda RELEASE firmware; WP-P-10 §4 step 4, §6)</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-002: Produce the release artifacts, including a panda RELEASE build with the LionDriver key and the reference lock</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-012</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    R3 Verify and assemble the evidence package (WP-P-10 §4 steps 5-8, §5)</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-003: Run and archive all required verification on the exact release commit</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-013</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    R4 Release decision and publication (WP-P-10 §4 steps 9-10)</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-004: Publish only the approved release through the LionDriver channel</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-020</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    I1 Incoming inspection (WP-O-01 INS-01..04)</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-005: Use only the approved, undamaged device and harness</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-021</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    I2 Vehicle preconditions (INS-05..08)</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-006: Install only on a vehicle that is in the reference configuration and healthy</t>
         </is>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-022</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    I3 Mechanical and electrical installation (INS-09..14)</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-007: Mount the device and connect the harness so that the CAN path, relay and camera view are as designed</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-023</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    I4 Provisioning: software, firmware, parameters (INS-15..20)</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-008: Provision the released software, panda firmware, models and parameter set</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-024</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    I5 Reference-configuration check (INS-21..24)</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-009: Confirm that the item identifies the vehicle as the reference configuration and runs the reference safety mode</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-025</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    I6 Calibration, functional check and driver briefing (INS-25..30)</t>
         </is>
       </c>
-      <c r="C12" s="42" t="inlineStr">
+      <c r="C12" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D12" s="42" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-010: Calibrate, prove the stock PCS path and engagement transitions, and brief the driver</t>
         </is>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-030</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    U1 Software update and rollback (WP-P-10 §8, WP-O-02)</t>
         </is>
       </c>
-      <c r="C13" s="42" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>process_step</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>PFM-SE-001</t>
         </is>
       </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>PFM-FN-011: Update or roll back only to an approved release whose evidence is valid for the installed device</t>
         </is>
